--- a/static/standards-correlations/ISTE_Standards.xlsx
+++ b/static/standards-correlations/ISTE_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$32</definedName>
@@ -550,10 +550,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | ISTE version 4.02</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | ISTE version 4.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -587,7 +588,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -640,7 +641,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Discovery Systems covers goal setting, ranking goals, and timeline feedback. Labs prompt reflection but do not formalize personal learning-goal setting.</t>
+          <t>Introductory Systems covers goal setting, ranking goals, and timeline feedback. Labs prompt reflection but do not formalize personal learning-goal setting.</t>
         </is>
       </c>
     </row>
@@ -777,7 +778,7 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>PreLabs cover the controller and the toolchain directly. Discovery Systems adds kit inventory, what qualifies as a robot, and the hardware/software split.</t>
+          <t>PreLabs cover the controller and the toolchain directly. Introductory Systems adds kit inventory, what qualifies as a robot, and the hardware/software split.</t>
         </is>
       </c>
     </row>
@@ -949,7 +950,7 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>Discovery Systems 10 covers what counts as personal information, how it is sought, and how to protect it.</t>
+          <t>Introductory Systems 10 covers what counts as personal information, how it is sought, and how to protect it.</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1181,7 @@
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>Discovery Systems teaches define-brainstorm-build-test-improve explicitly; labs apply decomposition and top-down planning.</t>
+          <t>Introductory Systems teaches define-brainstorm-build-test-improve explicitly; labs apply decomposition and top-down planning.</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1510,7 @@
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>The entire curriculum is autonomous robotics. Discovery Systems 3 addresses autonomy levels directly.</t>
+          <t>The entire curriculum is autonomous robotics. Introductory Systems 3 addresses autonomy levels directly.</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1819,7 @@
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>Discovery Systems 13 and 14 teach roles, goal ranking, and timelines. Botball team structure reinforces this throughout.</t>
+          <t>Introductory Systems 13 and 14 teach roles, goal ranking, and timelines. Botball team structure reinforces this throughout.</t>
         </is>
       </c>
     </row>
@@ -1899,6 +1900,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -1943,7 +1945,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1957,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -2043,6 +2045,8 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -2057,7 +2061,7 @@
 IMPORTANT: Indicator statements in column D are PARAPHRASED, not official ISTE text. Read the official statements at iste.org/standards/students. Review iste.org/permissions-licensing before distributing.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-This crosswalk scores against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+This crosswalk scores against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 An earlier revision of this file scored lab FRONT MATTER ONLY (headings, descriptions, concept tags, objectives) and materially undercounted coverage. Those figures are superseded.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?' in the labs), or where the standard is only partly met. Cells citing 'Ext N.NL' identify the specific extension carrying the evidence, so a reviewer can verify placement and decide whether optional work counts for their purposes.</t>
         </is>
